--- a/output/pdf_financials_xlsx/ARGH.xlsx
+++ b/output/pdf_financials_xlsx/ARGH.xlsx
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.038077</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003075</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="13">
@@ -1233,19 +1233,19 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-29.395923</v>
+        <v>-29.434</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-33.5066</v>
+        <v>-33.509675</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0.916045</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.797315</v>
+        <v>-3.801315</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-15.230124</v>
+        <v>-15.232424</v>
       </c>
     </row>
     <row r="28">
@@ -1293,19 +1293,19 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-24.303319</v>
+        <v>-24.341396</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-27.362259</v>
+        <v>-27.365334</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>2.303727</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.408547</v>
+        <v>-3.412547</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-14.810443</v>
+        <v>-14.812743</v>
       </c>
     </row>
     <row r="30">
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-95.62038947908601</v>
+        <v>-95.77020183887915</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-49.82087179072693</v>
+        <v>-49.826470713709</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>12.99152292903329</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-217.8173197048947</v>
+        <v>-218.0729328089004</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-670.5010543890927</v>
+        <v>-670.6051804051135</v>
       </c>
     </row>
     <row r="31">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.317861</v>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.317861</v>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
@@ -1610,10 +1610,10 @@
         <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.726112</v>
+        <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.115207</v>
+        <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0</v>
@@ -1640,10 +1640,10 @@
         <v>0.666679</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1.065626</v>
+        <v>0.339514</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.87448</v>
+        <v>0.759273</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>1.380661</v>
@@ -1853,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0</v>
+        <v>0.02898</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.142103</v>
@@ -7453,7 +7453,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OtherReceivables</t>
+          <t>AccountsReceivable</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -23574,7 +23574,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -29054,7 +29054,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">

--- a/output/pdf_financials_xlsx/ARGH.xlsx
+++ b/output/pdf_financials_xlsx/ARGH.xlsx
@@ -3745,13 +3745,13 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.883205</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>3.835026</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.145837</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -19242,7 +19242,11 @@
           <t>Proceeds from sale of property and equipment (Note 21)</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -20323,7 +20327,11 @@
           <t>Proceeds from sale of property and equipment (Note 20)</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ARGH.xlsx
+++ b/output/pdf_financials_xlsx/ARGH.xlsx
@@ -879,7 +879,7 @@
         <v>-33.5066</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.916045</v>
+        <v>0.9495130000000001</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-3.797315</v>
@@ -909,7 +909,7 @@
         <v>0.066124</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.033468</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0.06322700000000001</v>
@@ -1239,7 +1239,7 @@
         <v>-33.509675</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.916045</v>
+        <v>0.9495130000000001</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-3.801315</v>
@@ -1299,7 +1299,7 @@
         <v>-27.365334</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.303727</v>
+        <v>2.337195</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-3.412547</v>
@@ -1331,7 +1331,7 @@
         <v>-49.826470713709</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>12.99152292903329</v>
+        <v>13.18026069587324</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-218.0729328089004</v>
@@ -1361,7 +1361,7 @@
         <v>-0.1973461944810873</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>3.524754268767252</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-1.66504490673015</v>
@@ -1598,25 +1598,23 @@
       <c r="B40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C40" s="3" t="n">
+        <v>0.462983</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.743336</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.04998</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
     </row>
     <row r="41">
@@ -1634,19 +1632,19 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>1.915348</v>
+        <v>2.658684</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>0.666679</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.339514</v>
+        <v>0.389494</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0.759273</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1.380661</v>
+        <v>1.396261</v>
       </c>
     </row>
     <row r="42">
@@ -1844,7 +1842,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.363914</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.351324</v>
@@ -1856,7 +1854,7 @@
         <v>0.02898</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.142103</v>
+        <v>0.126503</v>
       </c>
     </row>
     <row r="49">
@@ -2424,25 +2422,23 @@
       <c r="B67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C67" s="3" t="n">
+        <v>0.5000329999999999</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.355087</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.810613</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.237243</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>2.448663</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>3.902962</v>
       </c>
     </row>
     <row r="68">
@@ -2520,19 +2516,19 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>8.718114</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>17.011068</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>3.496528</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.282485</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>1.014672</v>
       </c>
     </row>
     <row r="71">
@@ -2550,19 +2546,19 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>8.718114</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>17.011068</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>3.496528</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.282485</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>1.014672</v>
       </c>
     </row>
     <row r="72">
@@ -2670,19 +2666,19 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>3.163028</v>
+        <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>4.737563</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>4.268148</v>
+        <v>0.77162</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>5.619488</v>
+        <v>5.337003</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>3.391565</v>
+        <v>2.376893</v>
       </c>
     </row>
     <row r="76">
@@ -2823,30 +2819,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D80" s="3" t="n">
+        <v>0.8619966202818093</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>36.9660372766368</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>1.624586654846517</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.2360004611652108</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>-1.692671615647677</v>
       </c>
     </row>
     <row r="81">
@@ -3714,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.023322</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>-1.31361</v>
@@ -3854,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.56166</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -4376,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.023322</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>-1.31361</v>
@@ -4404,7 +4390,7 @@
         <v>-0.044536</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-9.590664</v>
+        <v>-9.613986000000001</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-21.200324</v>
@@ -5368,7 +5354,11 @@
           <t>Lease liabilities 27</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -6596,7 +6586,11 @@
           <t>Lease liabilities 28</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -10014,7 +10008,11 @@
           <t>Lease liabilities 30</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -10630,7 +10628,11 @@
           <t>Lease liabilities 29</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -11971,7 +11973,11 @@
           <t>Lease liabilities 34 8,718,114</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -13902,7 +13908,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -15220,7 +15230,11 @@
           <t>Shares issued for cash 22</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -16379,7 +16393,11 @@
           <t>Deferred income tax expense (recovery) 33</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -17989,7 +18007,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -18497,7 +18519,11 @@
           <t>Deferred income tax recovery (Note 32)</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -19193,7 +19219,11 @@
           <t>Purchase of equipment (Note 21)</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -21092,7 +21122,11 @@
           <t>Deferred income tax recovery (Note 10, 37)</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -21653,7 +21687,11 @@
           <t>Purchase of equipment (Note 25)</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -21702,7 +21740,11 @@
           <t>Purchase of intangible assets (Note 7)</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -26234,7 +26276,11 @@
           <t>Income tax recovery (expense) 32</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -26283,7 +26329,11 @@
           <t>Deferred income tax recovery 32</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -27775,7 +27825,11 @@
           <t>Deferred income tax recovery 32</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
           <t>-</t>
@@ -29427,7 +29481,11 @@
           <t>Deferred income tax recovery 10,37 294,623</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr">
         <is>
           <t>-</t>
